--- a/site/exports/ecnu-art.xlsx
+++ b/site/exports/ecnu-art.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,18 +443,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="62.99999999999999" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -569,10 +569,64 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>美术学院</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>所有现职unknown，导航false，不把名录或至今当人事证明。；张晓凌1979年仅毕业且层级未载，授位null；硕士博士明确获学位为true，但1990年为合并毕业背景，不能同时分配给两个授位或学习结束日期。；张晓凌目录特聘教授与个人页教授标签差异保留，不判断聘任类别。；4项作品只官网书目元数据；张晓凌条目未给作者名，作者归属仅个人页栏目上下文，不认定独著。；4个必要官方事实页可读，另有2次目录链接核验；不保存完整HTTP实体，不伪造HTTP200，页更新时间未知。；目录实际点击与重定向已核，原始HTML href属性未取。；学院法定行政上级/授位法人主体未独立查证。；来源差异/限制：profile：教授；directory_preview：特聘教授；两种原页标签并存，不据此判断正式聘任类别或当前在岗。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K3"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -584,12 +638,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40.59999999999999" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="57.4" customWidth="1" min="2" max="2"/>
+    <col width="22.4" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
@@ -601,9 +655,9 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="43.4" customWidth="1" min="15" max="15"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="62.99999999999999" customWidth="1" min="17" max="17"/>
+    <col width="65" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
@@ -666,7 +720,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1095,8 +1149,240 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>graduation_degree_level_and_award_unknown</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>高等教育（层级未载）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>安徽阜阳师范学院</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>仅毕业，未标本科、学士或学位；1979为毕业年，不作授位年。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源department：艺术系</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>硕士学位</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>中国艺术研究院</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>原文明确先后获硕士、博士学位，2项授位true；1990为合并叙述中的毕业年，不能同时赋给两段学习结束或两次授位，不补各段起止、专业或法定授位主体。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：硕士</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>博士学位</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>中国艺术研究院</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>原文明确先后获硕士、博士学位，2项授位true；1990为合并叙述中的毕业年，不能同时赋给两段学习结束或两次授位，不补各段起止、专业或法定授位主体。；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源education_stage：博士</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>教授，博士研究生、硕士研究生导师</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学美术学院</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S11"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1104,6 +1390,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1115,18 +1405,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="54.59999999999999" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1194,8 +1484,104 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>王朝闻</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>explicit_studied_under_stage_unassigned</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；只确认师从；不把两位分别或同时推为硕/博论文导师，不根据名人履历外推。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。；来源合述教育语境：中国艺术研究院硕士、博士经历合并叙述，未把导师逐一分配到具体阶段。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>刘纲纪</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>explicit_studied_under_stage_unassigned</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>来源记载的关系；本轮未进行学位论文原件及导师当前人事认证。；只确认师从；不把两位分别或同时推为硕/博论文导师，不根据名人履历外推。；原关系与阶段自述保留；未知不表示关系不存在，不建立现职身份导航。；来源合述教育语境：中国艺术研究院硕士、博士经历合并叙述，未把导师逐一分配到具体阶段。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L3"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1206,19 +1592,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16.8" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="62.99999999999999" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="62.99999999999999" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="62.99999999999999" customWidth="1" min="8" max="8"/>
     <col width="65" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
@@ -1397,8 +1783,112 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>中国原始艺术精神</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源书目信息（author_name_from_profile_context）：张晓凌</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>中国原始雕塑</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1998</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源书目信息（author_name_from_profile_context）：张晓凌</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1406,6 +1896,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1417,14 +1911,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40.59999999999999" customWidth="1" min="2" max="2"/>
-    <col width="62.99999999999999" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="33.59999999999999" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1532,11 +2026,87 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-ecnu-zhangxiaoling-s001-9b9b0d007909</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/c8/f1/c8827a182513/page.htm</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T23:45:29.642Z</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>张晓凌</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-ecnu-zhangxiaoling-s002-1e831723d36f</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://art.ecnu.edu.cn/dsml/list.htm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T23:45:27.328Z</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ecnu</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>华东师范大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
